--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/131.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/131.xlsx
@@ -426,13 +426,13 @@
         <v>-1.392713760970914</v>
       </c>
       <c r="E2">
-        <v>-19.89875249114164</v>
+        <v>-17.51563567974369</v>
       </c>
       <c r="F2">
-        <v>-1.738513867953094</v>
+        <v>-1.920789487999903</v>
       </c>
       <c r="G2">
-        <v>-8.581762336811853</v>
+        <v>-9.282507071023387</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.738515391846175</v>
       </c>
       <c r="E3">
-        <v>-20.67781187145297</v>
+        <v>-18.8064703723457</v>
       </c>
       <c r="F3">
-        <v>-1.987656133121282</v>
+        <v>-1.596607904914317</v>
       </c>
       <c r="G3">
-        <v>-9.204172984939328</v>
+        <v>-9.04293992585365</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.231124386283666</v>
       </c>
       <c r="E4">
-        <v>-21.01925152767845</v>
+        <v>-19.23611177747657</v>
       </c>
       <c r="F4">
-        <v>-1.851718557219675</v>
+        <v>-1.860547296998712</v>
       </c>
       <c r="G4">
-        <v>-8.493290729480501</v>
+        <v>-9.005085434654802</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.826252099167683</v>
       </c>
       <c r="E5">
-        <v>-21.5770070425463</v>
+        <v>-19.71678784336692</v>
       </c>
       <c r="F5">
-        <v>-1.487400916733647</v>
+        <v>-1.681164335922479</v>
       </c>
       <c r="G5">
-        <v>-9.018765736312236</v>
+        <v>-9.668495215841123</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.51295886278773</v>
       </c>
       <c r="E6">
-        <v>-22.39931381238308</v>
+        <v>-20.6954464067382</v>
       </c>
       <c r="F6">
-        <v>-1.419866607485611</v>
+        <v>-1.585855696025979</v>
       </c>
       <c r="G6">
-        <v>-9.231376943578729</v>
+        <v>-10.21119722085732</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.247250050915173</v>
       </c>
       <c r="E7">
-        <v>-24.26300924944134</v>
+        <v>-21.0254813446657</v>
       </c>
       <c r="F7">
-        <v>-2.340997077152814</v>
+        <v>-1.391325208622155</v>
       </c>
       <c r="G7">
-        <v>-8.981443837009977</v>
+        <v>-10.23657757439983</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.002378281044094</v>
       </c>
       <c r="E8">
-        <v>-23.78489156172708</v>
+        <v>-22.20241421668428</v>
       </c>
       <c r="F8">
-        <v>-0.6461747667404845</v>
+        <v>-1.489178593180055</v>
       </c>
       <c r="G8">
-        <v>-9.48745052142578</v>
+        <v>-10.31565050120317</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.738998754436945</v>
       </c>
       <c r="E9">
-        <v>-25.0119287751684</v>
+        <v>-22.09765776743813</v>
       </c>
       <c r="F9">
-        <v>-0.8811163295224803</v>
+        <v>-0.7879962363041767</v>
       </c>
       <c r="G9">
-        <v>-9.746542120020159</v>
+        <v>-10.47639535105031</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.415488398387454</v>
       </c>
       <c r="E10">
-        <v>-26.35963339044129</v>
+        <v>-23.28625285685684</v>
       </c>
       <c r="F10">
-        <v>-1.065887820553924</v>
+        <v>-0.7049747700934018</v>
       </c>
       <c r="G10">
-        <v>-10.9027325535237</v>
+        <v>-10.55681933817955</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.002807062426105</v>
       </c>
       <c r="E11">
-        <v>-27.85467317746246</v>
+        <v>-24.04180506106965</v>
       </c>
       <c r="F11">
-        <v>-0.6065257893728889</v>
+        <v>-0.6433649445101886</v>
       </c>
       <c r="G11">
-        <v>-8.862185024087921</v>
+        <v>-10.77679676130987</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.474060203610061</v>
       </c>
       <c r="E12">
-        <v>-27.62019947890794</v>
+        <v>-24.08368604406922</v>
       </c>
       <c r="F12">
-        <v>0.2928260729073119</v>
+        <v>-0.206968571204367</v>
       </c>
       <c r="G12">
-        <v>-9.082150698867581</v>
+        <v>-10.66461828771892</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.806917894176304</v>
       </c>
       <c r="E13">
-        <v>-29.39288974941656</v>
+        <v>-26.06748819943019</v>
       </c>
       <c r="F13">
-        <v>-0.3773894253497121</v>
+        <v>0.06363337990074466</v>
       </c>
       <c r="G13">
-        <v>-10.25997637279768</v>
+        <v>-10.33541122701331</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.999611204382997</v>
       </c>
       <c r="E14">
-        <v>-27.58177396773063</v>
+        <v>-25.74134482051406</v>
       </c>
       <c r="F14">
-        <v>-0.2945361177217056</v>
+        <v>0.4549823054749263</v>
       </c>
       <c r="G14">
-        <v>-9.321481571651821</v>
+        <v>-10.4526310484097</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.053504608760743</v>
       </c>
       <c r="E15">
-        <v>-29.75640787704483</v>
+        <v>-28.25145645119694</v>
       </c>
       <c r="F15">
-        <v>0.1913726036168452</v>
+        <v>0.4773697629029857</v>
       </c>
       <c r="G15">
-        <v>-9.459493362971843</v>
+        <v>-9.887799066866934</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.981727641702135</v>
       </c>
       <c r="E16">
-        <v>-30.64323063160149</v>
+        <v>-27.75179813294646</v>
       </c>
       <c r="F16">
-        <v>0.6885678308185393</v>
+        <v>0.827503268350878</v>
       </c>
       <c r="G16">
-        <v>-8.136745256789046</v>
+        <v>-9.275720440458787</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.81427488333109</v>
       </c>
       <c r="E17">
-        <v>-31.26405266043686</v>
+        <v>-28.78260441771228</v>
       </c>
       <c r="F17">
-        <v>0.9800338716979622</v>
+        <v>1.144045647247848</v>
       </c>
       <c r="G17">
-        <v>-8.051860812525884</v>
+        <v>-9.085093008021765</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.57766485088088</v>
       </c>
       <c r="E18">
-        <v>-32.65476793218968</v>
+        <v>-30.15364177420805</v>
       </c>
       <c r="F18">
-        <v>0.9307559516402252</v>
+        <v>1.740675612379386</v>
       </c>
       <c r="G18">
-        <v>-7.377314900286171</v>
+        <v>-8.052757603292932</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.308048771085894</v>
       </c>
       <c r="E19">
-        <v>-33.80909695157288</v>
+        <v>-30.98393516942248</v>
       </c>
       <c r="F19">
-        <v>1.562228706468316</v>
+        <v>1.842054528603601</v>
       </c>
       <c r="G19">
-        <v>-7.509087012033432</v>
+        <v>-8.154592306813896</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.04410371582111</v>
       </c>
       <c r="E20">
-        <v>-34.63757954664968</v>
+        <v>-31.90635925145557</v>
       </c>
       <c r="F20">
-        <v>1.573878865621289</v>
+        <v>2.349845403254503</v>
       </c>
       <c r="G20">
-        <v>-6.363306922586953</v>
+        <v>-7.333381290306917</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.805250771362315</v>
       </c>
       <c r="E21">
-        <v>-35.33242218432181</v>
+        <v>-32.79233059769064</v>
       </c>
       <c r="F21">
-        <v>1.865170949346123</v>
+        <v>2.895706387003265</v>
       </c>
       <c r="G21">
-        <v>-6.421095754111246</v>
+        <v>-7.06328148714411</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.618250410998194</v>
       </c>
       <c r="E22">
-        <v>-35.75672671290027</v>
+        <v>-33.81539529654699</v>
       </c>
       <c r="F22">
-        <v>2.464355599547896</v>
+        <v>3.021780592239739</v>
       </c>
       <c r="G22">
-        <v>-6.403838732363987</v>
+        <v>-6.845929167700155</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.497436021770608</v>
       </c>
       <c r="E23">
-        <v>-37.0146202098794</v>
+        <v>-33.78657200995268</v>
       </c>
       <c r="F23">
-        <v>2.345632326643865</v>
+        <v>3.34904370206374</v>
       </c>
       <c r="G23">
-        <v>-5.37559697515402</v>
+        <v>-6.562658158075181</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.436208453037988</v>
       </c>
       <c r="E24">
-        <v>-37.22736015357109</v>
+        <v>-35.28796621030084</v>
       </c>
       <c r="F24">
-        <v>3.16472035779721</v>
+        <v>3.604646404606361</v>
       </c>
       <c r="G24">
-        <v>-5.23032209238152</v>
+        <v>-5.315884024866077</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.43974094383411</v>
       </c>
       <c r="E25">
-        <v>-36.56989849442808</v>
+        <v>-35.1614905424315</v>
       </c>
       <c r="F25">
-        <v>3.179476894710681</v>
+        <v>3.399415067093172</v>
       </c>
       <c r="G25">
-        <v>-4.909934126904689</v>
+        <v>-5.88337896589178</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.496234260693996</v>
       </c>
       <c r="E26">
-        <v>-38.14700366062221</v>
+        <v>-35.08449208107484</v>
       </c>
       <c r="F26">
-        <v>2.726180998020346</v>
+        <v>4.264596774007893</v>
       </c>
       <c r="G26">
-        <v>-4.560237942648021</v>
+        <v>-5.739197985102958</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.581672432281019</v>
       </c>
       <c r="E27">
-        <v>-38.58004031601112</v>
+        <v>-36.08412228503084</v>
       </c>
       <c r="F27">
-        <v>2.993627697688195</v>
+        <v>4.146252893374345</v>
       </c>
       <c r="G27">
-        <v>-6.585214991342401</v>
+        <v>-6.26328146506763</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.688944142451169</v>
       </c>
       <c r="E28">
-        <v>-39.25097499269187</v>
+        <v>-36.37118186877468</v>
       </c>
       <c r="F28">
-        <v>3.303057714064728</v>
+        <v>3.756746256903989</v>
       </c>
       <c r="G28">
-        <v>-5.372586786640466</v>
+        <v>-6.604048902822692</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.796004401414424</v>
       </c>
       <c r="E29">
-        <v>-38.52567685637478</v>
+        <v>-35.88994304274981</v>
       </c>
       <c r="F29">
-        <v>3.368508679294722</v>
+        <v>3.623115684219179</v>
       </c>
       <c r="G29">
-        <v>-5.975266732520604</v>
+        <v>-5.917214215792608</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.883754032343578</v>
       </c>
       <c r="E30">
-        <v>-39.3553846487924</v>
+        <v>-36.25458876725276</v>
       </c>
       <c r="F30">
-        <v>2.833674922412027</v>
+        <v>3.493532514664446</v>
       </c>
       <c r="G30">
-        <v>-5.834738183414749</v>
+        <v>-6.608374906610166</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.946769682750912</v>
       </c>
       <c r="E31">
-        <v>-38.71500099461709</v>
+        <v>-35.64532720214005</v>
       </c>
       <c r="F31">
-        <v>2.847558360082947</v>
+        <v>3.528038987195462</v>
       </c>
       <c r="G31">
-        <v>-5.065278651565112</v>
+        <v>-5.959009625951741</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.969039759447248</v>
       </c>
       <c r="E32">
-        <v>-36.87294794177251</v>
+        <v>-35.53986470696868</v>
       </c>
       <c r="F32">
-        <v>2.086759229594991</v>
+        <v>3.233620644892462</v>
       </c>
       <c r="G32">
-        <v>-7.487302959165183</v>
+        <v>-6.413101654173257</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.943561599143149</v>
       </c>
       <c r="E33">
-        <v>-36.38845299806897</v>
+        <v>-35.36065779151365</v>
       </c>
       <c r="F33">
-        <v>2.54089674756657</v>
+        <v>2.942151290543428</v>
       </c>
       <c r="G33">
-        <v>-5.433278766150076</v>
+        <v>-6.344298091219057</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.869344048552811</v>
       </c>
       <c r="E34">
-        <v>-37.33358476302057</v>
+        <v>-35.06365749646384</v>
       </c>
       <c r="F34">
-        <v>2.226917337413862</v>
+        <v>3.041911576862572</v>
       </c>
       <c r="G34">
-        <v>-4.274014180890497</v>
+        <v>-6.615097573932283</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.736590132080068</v>
       </c>
       <c r="E35">
-        <v>-36.06692799014605</v>
+        <v>-34.26958633381891</v>
       </c>
       <c r="F35">
-        <v>2.025524654445246</v>
+        <v>2.98678206947146</v>
       </c>
       <c r="G35">
-        <v>-5.252197521310459</v>
+        <v>-6.143910390128157</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.54663902801288</v>
       </c>
       <c r="E36">
-        <v>-37.59952734378331</v>
+        <v>-34.36093829351417</v>
       </c>
       <c r="F36">
-        <v>1.753516963857584</v>
+        <v>2.468948068429016</v>
       </c>
       <c r="G36">
-        <v>-5.792585101246633</v>
+        <v>-6.221358128423533</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.299741879707891</v>
       </c>
       <c r="E37">
-        <v>-35.48279958336553</v>
+        <v>-33.68439055172792</v>
       </c>
       <c r="F37">
-        <v>1.690233007753313</v>
+        <v>2.442413803782542</v>
       </c>
       <c r="G37">
-        <v>-5.554681000381436</v>
+        <v>-5.721878305485513</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.990772945473888</v>
       </c>
       <c r="E38">
-        <v>-36.54680040964505</v>
+        <v>-33.05357174323368</v>
       </c>
       <c r="F38">
-        <v>1.969755647419172</v>
+        <v>2.388359517280263</v>
       </c>
       <c r="G38">
-        <v>-4.868676530131326</v>
+        <v>-5.901863037596862</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.628707350390665</v>
       </c>
       <c r="E39">
-        <v>-37.55122964928688</v>
+        <v>-32.60791347862862</v>
       </c>
       <c r="F39">
-        <v>1.710165184199474</v>
+        <v>1.919818346908807</v>
       </c>
       <c r="G39">
-        <v>-5.131962289911328</v>
+        <v>-5.635903875355561</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.220102184851124</v>
       </c>
       <c r="E40">
-        <v>-34.71760569906214</v>
+        <v>-31.80512264880721</v>
       </c>
       <c r="F40">
-        <v>1.950928513088345</v>
+        <v>2.047168237945592</v>
       </c>
       <c r="G40">
-        <v>-4.883453344517028</v>
+        <v>-5.307605353767657</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.769237592985908</v>
       </c>
       <c r="E41">
-        <v>-34.0060173133283</v>
+        <v>-32.54145586761438</v>
       </c>
       <c r="F41">
-        <v>1.272382952228769</v>
+        <v>1.687734651666469</v>
       </c>
       <c r="G41">
-        <v>-3.303073045966284</v>
+        <v>-4.866634927861075</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.291827739726125</v>
       </c>
       <c r="E42">
-        <v>-33.55509692997468</v>
+        <v>-31.98426934269803</v>
       </c>
       <c r="F42">
-        <v>1.470559912939717</v>
+        <v>1.684437749403327</v>
       </c>
       <c r="G42">
-        <v>-4.251185830185803</v>
+        <v>-3.976558995902006</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.795189632329365</v>
       </c>
       <c r="E43">
-        <v>-33.16154277804525</v>
+        <v>-30.68048909039653</v>
       </c>
       <c r="F43">
-        <v>1.420654090390658</v>
+        <v>1.598188135423843</v>
       </c>
       <c r="G43">
-        <v>-3.90879712003966</v>
+        <v>-4.439715529343867</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.285482096632284</v>
       </c>
       <c r="E44">
-        <v>-33.50017278680949</v>
+        <v>-31.07195417702957</v>
       </c>
       <c r="F44">
-        <v>1.682451324371414</v>
+        <v>1.238562367907271</v>
       </c>
       <c r="G44">
-        <v>-3.370364987802229</v>
+        <v>-4.076041418546377</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.775164328682466</v>
       </c>
       <c r="E45">
-        <v>-33.19573616688257</v>
+        <v>-30.55103349340163</v>
       </c>
       <c r="F45">
-        <v>1.072671855087836</v>
+        <v>1.62019620058142</v>
       </c>
       <c r="G45">
-        <v>-3.209535288755878</v>
+        <v>-4.303742729549504</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.26912082403815</v>
       </c>
       <c r="E46">
-        <v>-33.65253126765516</v>
+        <v>-31.24283805698964</v>
       </c>
       <c r="F46">
-        <v>1.619942720156163</v>
+        <v>1.122789739692012</v>
       </c>
       <c r="G46">
-        <v>-3.829143302564794</v>
+        <v>-3.717586186186523</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.775104100401981</v>
       </c>
       <c r="E47">
-        <v>-32.92113829371888</v>
+        <v>-29.4319548551379</v>
       </c>
       <c r="F47">
-        <v>1.659555249358036</v>
+        <v>1.157801516338736</v>
       </c>
       <c r="G47">
-        <v>-2.636881516418134</v>
+        <v>-3.098991141278959</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.304167302436479</v>
       </c>
       <c r="E48">
-        <v>-32.42522409547772</v>
+        <v>-29.1622307754639</v>
       </c>
       <c r="F48">
-        <v>0.7551056140810067</v>
+        <v>1.21373619684537</v>
       </c>
       <c r="G48">
-        <v>-4.182413596166697</v>
+        <v>-3.500881331401165</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.8619750800455843</v>
       </c>
       <c r="E49">
-        <v>-31.62275098632267</v>
+        <v>-28.08209264658176</v>
       </c>
       <c r="F49">
-        <v>0.6737491663498589</v>
+        <v>1.252613135793556</v>
       </c>
       <c r="G49">
-        <v>-3.276404289968062</v>
+        <v>-3.334302772765181</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.4595610821761263</v>
       </c>
       <c r="E50">
-        <v>-31.70946796217942</v>
+        <v>-28.50339232676671</v>
       </c>
       <c r="F50">
-        <v>0.7527480804526394</v>
+        <v>1.064320254932812</v>
       </c>
       <c r="G50">
-        <v>-3.260564902533778</v>
+        <v>-3.176994968172242</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.1074400415921266</v>
       </c>
       <c r="E51">
-        <v>-31.01126329993985</v>
+        <v>-27.18000476380069</v>
       </c>
       <c r="F51">
-        <v>0.7385299823509887</v>
+        <v>0.9630109215704323</v>
       </c>
       <c r="G51">
-        <v>-2.603377831080377</v>
+        <v>-3.333600482470172</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.1882638442306376</v>
       </c>
       <c r="E52">
-        <v>-30.80156973675492</v>
+        <v>-27.80847285468507</v>
       </c>
       <c r="F52">
-        <v>0.6645542881787845</v>
+        <v>1.084244147704946</v>
       </c>
       <c r="G52">
-        <v>-2.380605605865271</v>
+        <v>-3.184453865469052</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.4155859683614707</v>
       </c>
       <c r="E53">
-        <v>-28.03415835807625</v>
+        <v>-27.0459515618692</v>
       </c>
       <c r="F53">
-        <v>0.7354981576567425</v>
+        <v>0.9881237077537021</v>
       </c>
       <c r="G53">
-        <v>-3.557377844352856</v>
+        <v>-3.340988889663023</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.5670464841868147</v>
       </c>
       <c r="E54">
-        <v>-28.47039921600227</v>
+        <v>-26.64060644298858</v>
       </c>
       <c r="F54">
-        <v>0.4745069251589106</v>
+        <v>0.5758518783196106</v>
       </c>
       <c r="G54">
-        <v>-2.39980763233291</v>
+        <v>-3.091002262830152</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.6417783925728027</v>
       </c>
       <c r="E55">
-        <v>-28.89833780448995</v>
+        <v>-25.37297574205839</v>
       </c>
       <c r="F55">
-        <v>0.6103252161545148</v>
+        <v>0.5641669277357207</v>
       </c>
       <c r="G55">
-        <v>-3.072473808467021</v>
+        <v>-3.701258589513701</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.6387100413514263</v>
       </c>
       <c r="E56">
-        <v>-27.14558710155184</v>
+        <v>-25.37982438753303</v>
       </c>
       <c r="F56">
-        <v>0.1875728823402039</v>
+        <v>0.7637471428270113</v>
       </c>
       <c r="G56">
-        <v>-3.454793857134242</v>
+        <v>-3.540032057289499</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.566333503954131</v>
       </c>
       <c r="E57">
-        <v>-27.37697496409201</v>
+        <v>-24.7308228198587</v>
       </c>
       <c r="F57">
-        <v>0.816401488418559</v>
+        <v>0.2813333035608716</v>
       </c>
       <c r="G57">
-        <v>-2.356860883809096</v>
+        <v>-3.771555498374017</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.4381009638865617</v>
       </c>
       <c r="E58">
-        <v>-26.06145358337522</v>
+        <v>-24.91884284974502</v>
       </c>
       <c r="F58">
-        <v>0.9575635775296227</v>
+        <v>0.5282340065370837</v>
       </c>
       <c r="G58">
-        <v>-3.215845458432598</v>
+        <v>-4.023278270359977</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.2664159561205232</v>
       </c>
       <c r="E59">
-        <v>-26.08443745484682</v>
+        <v>-24.09857945988005</v>
       </c>
       <c r="F59">
-        <v>0.4592740769888305</v>
+        <v>0.2085827647774078</v>
       </c>
       <c r="G59">
-        <v>-3.829730720097794</v>
+        <v>-4.226370702847271</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.06606580137476022</v>
       </c>
       <c r="E60">
-        <v>-25.56948908910398</v>
+        <v>-23.47095862410594</v>
       </c>
       <c r="F60">
-        <v>0.07726499388121333</v>
+        <v>0.7429484940775213</v>
       </c>
       <c r="G60">
-        <v>-3.055370820650638</v>
+        <v>-4.15721207862868</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.1499658542483989</v>
       </c>
       <c r="E61">
-        <v>-26.43644288068266</v>
+        <v>-23.48765453363175</v>
       </c>
       <c r="F61">
-        <v>0.4019021790383396</v>
+        <v>0.1360931617258258</v>
       </c>
       <c r="G61">
-        <v>-4.53885072295762</v>
+        <v>-4.350884944631237</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.3697008730529519</v>
       </c>
       <c r="E62">
-        <v>-26.54416056960342</v>
+        <v>-23.21677378460378</v>
       </c>
       <c r="F62">
-        <v>-0.1114404139461252</v>
+        <v>0.3848021907423494</v>
       </c>
       <c r="G62">
-        <v>-4.726529319378981</v>
+        <v>-4.830053174650396</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.5811616960089466</v>
       </c>
       <c r="E63">
-        <v>-25.01523473138296</v>
+        <v>-21.33167684958868</v>
       </c>
       <c r="F63">
-        <v>0.4620698169732789</v>
+        <v>-0.3649929071668175</v>
       </c>
       <c r="G63">
-        <v>-4.960055201564883</v>
+        <v>-5.120323590524145</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.7738991489939948</v>
       </c>
       <c r="E64">
-        <v>-24.25854039405582</v>
+        <v>-21.74133300182447</v>
       </c>
       <c r="F64">
-        <v>0.2635913305277117</v>
+        <v>-0.4826036826488885</v>
       </c>
       <c r="G64">
-        <v>-4.838125596926119</v>
+        <v>-5.985965563854986</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.9375238349236182</v>
       </c>
       <c r="E65">
-        <v>-23.30434009217647</v>
+        <v>-21.61885064664395</v>
       </c>
       <c r="F65">
-        <v>0.2485224991033859</v>
+        <v>-0.07183368331607248</v>
       </c>
       <c r="G65">
-        <v>-6.412185282821777</v>
+        <v>-5.880298287274266</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.062875853782057</v>
       </c>
       <c r="E66">
-        <v>-23.84686993432749</v>
+        <v>-22.01204346918812</v>
       </c>
       <c r="F66">
-        <v>-0.07763722534008581</v>
+        <v>-0.2589974994068012</v>
       </c>
       <c r="G66">
-        <v>-5.507935618477552</v>
+        <v>-5.641462150590041</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.141155996679613</v>
       </c>
       <c r="E67">
-        <v>-26.1072344318088</v>
+        <v>-21.05769780491239</v>
       </c>
       <c r="F67">
-        <v>-0.129360485970887</v>
+        <v>-0.5252165585837006</v>
       </c>
       <c r="G67">
-        <v>-4.877401638554827</v>
+        <v>-5.525077767462802</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.165836692213565</v>
       </c>
       <c r="E68">
-        <v>-25.83924016465159</v>
+        <v>-22.1523347945295</v>
       </c>
       <c r="F68">
-        <v>-0.4710057106422926</v>
+        <v>-0.4142857378378049</v>
       </c>
       <c r="G68">
-        <v>-5.940379352549557</v>
+        <v>-6.112362152489144</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.134109837728122</v>
       </c>
       <c r="E69">
-        <v>-23.57071876012832</v>
+        <v>-20.83170496388317</v>
       </c>
       <c r="F69">
-        <v>-0.5320307088391294</v>
+        <v>-1.2300743816258</v>
       </c>
       <c r="G69">
-        <v>-5.643412376799603</v>
+        <v>-6.02933525300256</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.042888322955366</v>
       </c>
       <c r="E70">
-        <v>-24.72241256692593</v>
+        <v>-20.82461127894036</v>
       </c>
       <c r="F70">
-        <v>-0.7835777245776441</v>
+        <v>-1.205580385892421</v>
       </c>
       <c r="G70">
-        <v>-5.842810605690471</v>
+        <v>-5.821070935480271</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.8925836512793907</v>
       </c>
       <c r="E71">
-        <v>-22.55100985602244</v>
+        <v>-20.8982518689409</v>
       </c>
       <c r="F71">
-        <v>-0.6608625491595226</v>
+        <v>-1.396809000828687</v>
       </c>
       <c r="G71">
-        <v>-5.547799077639261</v>
+        <v>-5.989419578949029</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.686027625118818</v>
       </c>
       <c r="E72">
-        <v>-24.45032738661376</v>
+        <v>-20.2701824863437</v>
       </c>
       <c r="F72">
-        <v>-1.022772953973015</v>
+        <v>-1.280463142370691</v>
       </c>
       <c r="G72">
-        <v>-6.34043418922421</v>
+        <v>-6.118259824520469</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.4250674653193703</v>
       </c>
       <c r="E73">
-        <v>-25.53104696508137</v>
+        <v>-20.58448505977275</v>
       </c>
       <c r="F73">
-        <v>-1.159721138106038</v>
+        <v>-1.279163433915699</v>
       </c>
       <c r="G73">
-        <v>-4.255859063003895</v>
+        <v>-5.534458172778672</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.1157020064538805</v>
       </c>
       <c r="E74">
-        <v>-24.28395389415245</v>
+        <v>-21.96414448297887</v>
       </c>
       <c r="F74">
-        <v>-1.337815159503515</v>
+        <v>-1.434168370694945</v>
       </c>
       <c r="G74">
-        <v>-5.024898264974363</v>
+        <v>-5.295308746743513</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.2367090838130461</v>
       </c>
       <c r="E75">
-        <v>-23.64248625182136</v>
+        <v>-21.16741734169171</v>
       </c>
       <c r="F75">
-        <v>-0.8241693840496255</v>
+        <v>-1.561929131963518</v>
       </c>
       <c r="G75">
-        <v>-4.245914736856346</v>
+        <v>-5.197580744464369</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.6282135296229279</v>
       </c>
       <c r="E76">
-        <v>-23.86411406774818</v>
+        <v>-21.38496255088623</v>
       </c>
       <c r="F76">
-        <v>-1.919440905868146</v>
+        <v>-1.84045524564381</v>
       </c>
       <c r="G76">
-        <v>-3.615312877574251</v>
+        <v>-5.063443298117559</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.050255254480199</v>
       </c>
       <c r="E77">
-        <v>-23.14568741956802</v>
+        <v>-22.05212195847271</v>
       </c>
       <c r="F77">
-        <v>-1.502328097332094</v>
+        <v>-1.871871907762384</v>
       </c>
       <c r="G77">
-        <v>-4.111983539332233</v>
+        <v>-4.527843823761486</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.497579408199837</v>
       </c>
       <c r="E78">
-        <v>-25.33336241244218</v>
+        <v>-22.06179894085956</v>
       </c>
       <c r="F78">
-        <v>-2.064018353780952</v>
+        <v>-1.761146522132383</v>
       </c>
       <c r="G78">
-        <v>-3.288212687753667</v>
+        <v>-4.483307131781685</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.964093033786036</v>
       </c>
       <c r="E79">
-        <v>-25.0476920778865</v>
+        <v>-22.48181320213947</v>
       </c>
       <c r="F79">
-        <v>-2.296100392288484</v>
+        <v>-2.317187312894148</v>
       </c>
       <c r="G79">
-        <v>-2.547121506631068</v>
+        <v>-4.028228242104729</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.437823919882777</v>
       </c>
       <c r="E80">
-        <v>-24.92547968144209</v>
+        <v>-22.61176718449336</v>
       </c>
       <c r="F80">
-        <v>-1.227546204312456</v>
+        <v>-2.097364283580646</v>
       </c>
       <c r="G80">
-        <v>-3.226734874122132</v>
+        <v>-3.67977738301802</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.911677240165782</v>
       </c>
       <c r="E81">
-        <v>-28.15178560921805</v>
+        <v>-23.13699059505382</v>
       </c>
       <c r="F81">
-        <v>-1.970085632140502</v>
+        <v>-2.093285402489261</v>
       </c>
       <c r="G81">
-        <v>-2.969485155836784</v>
+        <v>-3.355214836939999</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.373866658465762</v>
       </c>
       <c r="E82">
-        <v>-25.50019691136054</v>
+        <v>-24.01515390399822</v>
       </c>
       <c r="F82">
-        <v>-2.46996891156428</v>
+        <v>-1.841662176949689</v>
       </c>
       <c r="G82">
-        <v>-2.619548783077733</v>
+        <v>-3.022023779988348</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.807984985696232</v>
       </c>
       <c r="E83">
-        <v>-26.55861374501382</v>
+        <v>-25.5017128334941</v>
       </c>
       <c r="F83">
-        <v>-2.409799616894535</v>
+        <v>-2.082326930117627</v>
       </c>
       <c r="G83">
-        <v>-1.597079382158717</v>
+        <v>-2.245504794764341</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.200779345711818</v>
       </c>
       <c r="E84">
-        <v>-28.79251397993332</v>
+        <v>-25.27433697309371</v>
       </c>
       <c r="F84">
-        <v>-2.209358728071736</v>
+        <v>-2.478138270890689</v>
       </c>
       <c r="G84">
-        <v>-2.043986641265489</v>
+        <v>-2.580288405916571</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.535794616942243</v>
       </c>
       <c r="E85">
-        <v>-30.23956341009611</v>
+        <v>-27.49468943267162</v>
       </c>
       <c r="F85">
-        <v>-1.968428897334903</v>
+        <v>-2.20075199075665</v>
       </c>
       <c r="G85">
-        <v>-1.601817883591587</v>
+        <v>-2.589640093041939</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.796358463440635</v>
       </c>
       <c r="E86">
-        <v>-29.94183007324746</v>
+        <v>-27.55415926563185</v>
       </c>
       <c r="F86">
-        <v>-2.1793734848252</v>
+        <v>-2.128529122008769</v>
       </c>
       <c r="G86">
-        <v>-1.060853329100777</v>
+        <v>-2.035308526244628</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.969470987454796</v>
       </c>
       <c r="E87">
-        <v>-29.53757101912829</v>
+        <v>-29.39749981398712</v>
       </c>
       <c r="F87">
-        <v>-1.658370978467048</v>
+        <v>-2.175885229692011</v>
       </c>
       <c r="G87">
-        <v>-1.683369712384193</v>
+        <v>-1.824741531992977</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.041984597122269</v>
       </c>
       <c r="E88">
-        <v>-31.36084325036199</v>
+        <v>-30.06739826444233</v>
       </c>
       <c r="F88">
-        <v>-2.670932500218246</v>
+        <v>-2.480163629190534</v>
       </c>
       <c r="G88">
-        <v>-2.212348338457203</v>
+        <v>-2.691412138692717</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.00421519172684</v>
       </c>
       <c r="E89">
-        <v>-32.00899963953172</v>
+        <v>-30.70004656252515</v>
       </c>
       <c r="F89">
-        <v>-2.221848023403744</v>
+        <v>-2.145634908876579</v>
       </c>
       <c r="G89">
-        <v>-1.963753238491395</v>
+        <v>-2.189561759665966</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.850872561429158</v>
       </c>
       <c r="E90">
-        <v>-35.08832134191633</v>
+        <v>-33.49343835464628</v>
       </c>
       <c r="F90">
-        <v>-2.341347476564198</v>
+        <v>-2.254552796833672</v>
       </c>
       <c r="G90">
-        <v>-1.076102688257469</v>
+        <v>-2.323015190929904</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.579629983644304</v>
       </c>
       <c r="E91">
-        <v>-34.30929934050692</v>
+        <v>-34.42505141673556</v>
       </c>
       <c r="F91">
-        <v>-2.303251688076852</v>
+        <v>-2.290977768269572</v>
       </c>
       <c r="G91">
-        <v>-1.904572880100039</v>
+        <v>-2.768371667749554</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.191755270136225</v>
       </c>
       <c r="E92">
-        <v>-37.18706362069194</v>
+        <v>-35.63254569428789</v>
       </c>
       <c r="F92">
-        <v>-2.364757967734715</v>
+        <v>-2.183609755723117</v>
       </c>
       <c r="G92">
-        <v>-1.657243991260922</v>
+        <v>-2.413801223341277</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.691892909290204</v>
       </c>
       <c r="E93">
-        <v>-38.28464523713836</v>
+        <v>-38.22077507677948</v>
       </c>
       <c r="F93">
-        <v>-2.115184951517072</v>
+        <v>-2.020735328617275</v>
       </c>
       <c r="G93">
-        <v>-3.279484968585576</v>
+        <v>-2.74462955643797</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.089456161631681</v>
       </c>
       <c r="E94">
-        <v>-40.2121713790479</v>
+        <v>-39.10340101129241</v>
       </c>
       <c r="F94">
-        <v>-2.0878819619208</v>
+        <v>-2.02287914345572</v>
       </c>
       <c r="G94">
-        <v>-1.537658835264978</v>
+        <v>-2.989676654504454</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.398490951738975</v>
       </c>
       <c r="E95">
-        <v>-40.43518636755722</v>
+        <v>-41.38290765976985</v>
       </c>
       <c r="F95">
-        <v>-3.038759105022533</v>
+        <v>-1.865623532443067</v>
       </c>
       <c r="G95">
-        <v>-4.041133152618602</v>
+        <v>-3.988631078891313</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.628324560164623</v>
       </c>
       <c r="E96">
-        <v>-44.62006800534324</v>
+        <v>-43.56482007193081</v>
       </c>
       <c r="F96">
-        <v>-2.924042645245843</v>
+        <v>-1.974984596960658</v>
       </c>
       <c r="G96">
-        <v>-3.246190142815108</v>
+        <v>-3.758373848933486</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.8042476867052291</v>
       </c>
       <c r="E97">
-        <v>-46.61327926096062</v>
+        <v>-44.38541779530742</v>
       </c>
       <c r="F97">
-        <v>-2.499135727816851</v>
+        <v>-1.687462413285964</v>
       </c>
       <c r="G97">
-        <v>-3.267827993986255</v>
+        <v>-4.472963361711694</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.07237340937967721</v>
       </c>
       <c r="E98">
-        <v>-47.6059954063636</v>
+        <v>-46.95489958187873</v>
       </c>
       <c r="F98">
-        <v>-1.781797721484174</v>
+        <v>-1.443324315598088</v>
       </c>
       <c r="G98">
-        <v>-4.042120014074042</v>
+        <v>-5.187049000783818</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.9575684673608597</v>
       </c>
       <c r="E99">
-        <v>-49.46281312546795</v>
+        <v>-49.22637495795679</v>
       </c>
       <c r="F99">
-        <v>-1.556866978765011</v>
+        <v>-1.554386846761029</v>
       </c>
       <c r="G99">
-        <v>-5.507854685395228</v>
+        <v>-5.071797680809122</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.876195153389065</v>
       </c>
       <c r="E100">
-        <v>-50.49768228921229</v>
+        <v>-51.09686089553114</v>
       </c>
       <c r="F100">
-        <v>-1.967711531164078</v>
+        <v>-1.249270139450873</v>
       </c>
       <c r="G100">
-        <v>-5.143397351220404</v>
+        <v>-6.027669597953429</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.742996093581459</v>
       </c>
       <c r="E101">
-        <v>-51.92970540080184</v>
+        <v>-53.89061194043187</v>
       </c>
       <c r="F101">
-        <v>-1.088845194755109</v>
+        <v>-0.8816829328259952</v>
       </c>
       <c r="G101">
-        <v>-5.955422462883551</v>
+        <v>-5.855188145796939</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.653378213459835</v>
       </c>
       <c r="E102">
-        <v>-55.21268553116499</v>
+        <v>-55.417091537182</v>
       </c>
       <c r="F102">
-        <v>-1.902785750867459</v>
+        <v>-0.7184953828418953</v>
       </c>
       <c r="G102">
-        <v>-5.56843440288742</v>
+        <v>-6.696372663798231</v>
       </c>
     </row>
   </sheetData>
